--- a/老虎机数学专题-巨型图案.xlsx
+++ b/老虎机数学专题-巨型图案.xlsx
@@ -3836,6 +3836,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Y88" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6555,5 +6558,8 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:O102" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机数学专题-巨型图案.xlsx
+++ b/老虎机数学专题-巨型图案.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="巨型图案 类型一+类型二→RTP" sheetId="8" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="141">
   <si>
     <t>巨型图案 Mega Symbol</t>
   </si>
@@ -1155,7 +1155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1216,6 +1216,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2390,1422 +2416,1422 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:10">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="22" t="s">
+      <c r="B22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="22" t="s">
+      <c r="A23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:10">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="22" t="s">
+      <c r="B24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:10">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="22" t="s">
+      <c r="B25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:10">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="22" t="s">
+      <c r="B26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:10">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="22" t="s">
+      <c r="B27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="22" t="s">
+      <c r="A28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:10">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="22" t="s">
+      <c r="B29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:10">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="22" t="s">
+      <c r="B30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:10">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="22" t="s">
+      <c r="B31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="22" t="s">
+      <c r="A32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="22" t="s">
+      <c r="B33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="22" t="s">
+      <c r="B34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:10">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="22" t="s">
+      <c r="B35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:10">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="22" t="s">
+      <c r="E36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="14.5" spans="1:10">
-      <c r="A37" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="31" t="s">
+      <c r="A37" s="41">
+        <v>1</v>
+      </c>
+      <c r="B37" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="22" t="s">
+      <c r="E37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="14.5" spans="1:10">
-      <c r="A38" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="31" t="s">
+      <c r="A38" s="41">
+        <v>2</v>
+      </c>
+      <c r="B38" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="42" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="39" ht="29" spans="1:10">
-      <c r="A39" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="31" t="s">
+      <c r="A39" s="41">
+        <v>3</v>
+      </c>
+      <c r="B39" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="42" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1" spans="1:10">
-      <c r="A40" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="30" t="s">
+      <c r="A40" s="41">
+        <v>4</v>
+      </c>
+      <c r="B40" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="22" t="s">
+      <c r="E40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1" spans="1:10">
-      <c r="A41" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="30" t="s">
+      <c r="A41" s="41">
+        <v>5</v>
+      </c>
+      <c r="B41" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="22" t="s">
+      <c r="E41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1" spans="1:10">
-      <c r="A42" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="30" t="s">
+      <c r="A42" s="41">
+        <v>6</v>
+      </c>
+      <c r="B42" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="E42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="22" t="s">
+      <c r="E42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="22" t="s">
+      <c r="A43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:10">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="22" t="s">
+      <c r="B44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="22" t="s">
+      <c r="B45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:10">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="22" t="s">
+      <c r="B46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="22" t="s">
+      <c r="A47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:10">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="22" t="s">
+      <c r="B48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:10">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="22" t="s">
+      <c r="B49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:10">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="22" t="s">
+      <c r="B50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:10">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="22" t="s">
+      <c r="B51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="22" t="s">
+      <c r="A52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:10">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="22" t="s">
+      <c r="B53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:10">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="22" t="s">
+      <c r="B54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:10">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="22" t="s">
+      <c r="C55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="14.5" spans="1:10">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="42" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="57" ht="14.5" spans="1:10">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B57" s="31" t="s">
+      <c r="B57" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="C57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="22" t="s">
+      <c r="C57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="22" t="s">
+      <c r="A58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:10">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="22" t="s">
+      <c r="B59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="22" t="s">
+      <c r="A60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" spans="1:10">
-      <c r="A61" s="28" t="s">
+      <c r="A61" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="22" t="s">
+      <c r="C61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="14.5" spans="1:10">
-      <c r="A62" s="30" t="s">
+      <c r="A62" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="31" t="s">
+      <c r="B62" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="22" t="s">
+      <c r="C62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="14.5" spans="1:10">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="B63" s="31" t="s">
+      <c r="B63" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="C63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="22" t="s">
+      <c r="C63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="14.5" spans="1:10">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="31" t="s">
+      <c r="B64" s="42" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="65" ht="14.5" spans="1:10">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="31" t="s">
+      <c r="B65" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C65" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="22" t="s">
+      <c r="C65" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="14.5" spans="1:10">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="31" t="s">
+      <c r="B66" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="22" t="s">
+      <c r="C66" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="14.5" spans="1:10">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B67" s="31" t="s">
+      <c r="B67" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C67" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="22" t="s">
+      <c r="C67" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="14.5" spans="1:10">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B68" s="31" t="s">
+      <c r="B68" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="22" t="s">
+      <c r="C68" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4115,8 +4141,8 @@
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="4" t="s">
-        <v>87</v>
+      <c r="A9" s="43">
+        <v>10</v>
       </c>
       <c r="B9" s="8">
         <v>4</v>
@@ -4147,8 +4173,8 @@
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="4" t="s">
-        <v>88</v>
+      <c r="A10" s="43">
+        <v>9</v>
       </c>
       <c r="B10" s="8">
         <v>4</v>
@@ -4467,8 +4493,8 @@
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:10">
-      <c r="A20" s="4" t="s">
-        <v>87</v>
+      <c r="A20" s="43">
+        <v>10</v>
       </c>
       <c r="B20" s="8">
         <v>3</v>
@@ -4499,8 +4525,8 @@
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:10">
-      <c r="A21" s="4" t="s">
-        <v>88</v>
+      <c r="A21" s="43">
+        <v>9</v>
       </c>
       <c r="B21" s="8">
         <v>2</v>
@@ -5552,8 +5578,8 @@
       <c r="D53" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>115</v>
+      <c r="E53" s="43">
+        <v>100</v>
       </c>
       <c r="F53" s="9">
         <f>D27</f>
@@ -5616,14 +5642,14 @@
       <c r="B55" s="10">
         <v>0.2</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>120</v>
+      <c r="C55" s="43">
+        <v>111</v>
+      </c>
+      <c r="D55" s="43">
+        <v>101</v>
+      </c>
+      <c r="E55" s="43">
+        <v>110</v>
       </c>
       <c r="F55" s="9">
         <f>D34</f>
@@ -5651,11 +5677,11 @@
       <c r="B56" s="10">
         <v>0.2</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>118</v>
+      <c r="C56" s="43">
+        <v>111</v>
+      </c>
+      <c r="D56" s="43">
+        <v>111</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>121</v>
@@ -5686,14 +5712,14 @@
       <c r="B57" s="10">
         <v>0.2</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>118</v>
+      <c r="C57" s="43">
+        <v>111</v>
+      </c>
+      <c r="D57" s="43">
+        <v>111</v>
+      </c>
+      <c r="E57" s="43">
+        <v>111</v>
       </c>
       <c r="F57" s="9">
         <f>D34</f>
@@ -6241,8 +6267,8 @@
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:10">
-      <c r="A74" s="4" t="s">
-        <v>87</v>
+      <c r="A74" s="43">
+        <v>10</v>
       </c>
       <c r="B74" s="8">
         <v>4</v>
@@ -6276,8 +6302,8 @@
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:10">
-      <c r="A75" s="4" t="s">
-        <v>88</v>
+      <c r="A75" s="43">
+        <v>9</v>
       </c>
       <c r="B75" s="8">
         <v>4</v>
